--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 6.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 6.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Penjualan 6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C420DCDE-008E-4682-916A-F1077BDD2FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="3" r:id="rId1"/>
@@ -25,7 +24,7 @@
     <definedName name="negara">#REF!</definedName>
     <definedName name="UKURAN">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -218,7 +217,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -386,6 +385,9 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -396,9 +398,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -427,9 +426,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -467,9 +466,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -504,7 +503,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -539,7 +538,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -712,7 +711,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -735,20 +734,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -790,20 +789,38 @@
       <c r="C4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="11" t="str">
+        <f>VLOOKUP(MID(B4,4,2),$M$5:$N$9,2,FALSE)</f>
+        <v>LG</v>
+      </c>
       <c r="E4" s="4">
         <v>4</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="M4" s="16" t="s">
+      <c r="G4" s="11">
+        <f>INDEX($H$17:$L$20,MATCH(MID(B4,6,2),$H$17:$H$20,0),MATCH(VLOOKUP(MID(B4,4,2),$M$5:$N$9,2,FALSE),$H$17:$L$17,0))</f>
+        <v>3500000</v>
+      </c>
+      <c r="H4" s="12">
+        <f>G4*E4</f>
+        <v>14000000</v>
+      </c>
+      <c r="I4" s="11" t="str">
+        <f>HLOOKUP(LEFT(B4,3),$B$16:$F$18,2,FALSE)</f>
+        <v>BEKASI</v>
+      </c>
+      <c r="J4" s="12">
+        <f>HLOOKUP(LEFT(B4,3),$B$16:$F$18,3,FALSE)</f>
+        <v>150000</v>
+      </c>
+      <c r="K4" s="12">
+        <f>H4+J4</f>
+        <v>14150000</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="16"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
@@ -812,16 +829,34 @@
       <c r="C5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11" t="str">
+        <f t="shared" ref="D5:D13" si="0">VLOOKUP(MID(B5,4,2),$M$5:$N$9,2,FALSE)</f>
+        <v>SHARP</v>
+      </c>
       <c r="E5" s="4">
         <v>4</v>
       </c>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="G5" s="11">
+        <f t="shared" ref="G5:G13" si="1">INDEX($H$17:$L$20,MATCH(MID(B5,6,2),$H$17:$H$20,0),MATCH(VLOOKUP(MID(B5,4,2),$M$5:$N$9,2,FALSE),$H$17:$L$17,0))</f>
+        <v>2250000</v>
+      </c>
+      <c r="H5" s="12">
+        <f t="shared" ref="H5:H13" si="2">G5*E5</f>
+        <v>9000000</v>
+      </c>
+      <c r="I5" s="11" t="str">
+        <f t="shared" ref="I5:I13" si="3">HLOOKUP(LEFT(B5,3),$B$16:$F$18,2,FALSE)</f>
+        <v>JAKARTA</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" ref="J5:J13" si="4">HLOOKUP(LEFT(B5,3),$B$16:$F$18,3,FALSE)</f>
+        <v>50000</v>
+      </c>
+      <c r="K5" s="12">
+        <f t="shared" ref="K5:K13" si="5">H5+J5</f>
+        <v>9050000</v>
+      </c>
       <c r="M5" s="7" t="s">
         <v>12</v>
       </c>
@@ -836,16 +871,34 @@
       <c r="C6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SAMSUNG</v>
+      </c>
       <c r="E6" s="4">
         <v>3</v>
       </c>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="G6" s="11">
+        <f t="shared" si="1"/>
+        <v>1600000</v>
+      </c>
+      <c r="H6" s="12">
+        <f t="shared" si="2"/>
+        <v>4800000</v>
+      </c>
+      <c r="I6" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>BOGOR</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="K6" s="12">
+        <f t="shared" si="5"/>
+        <v>4900000</v>
+      </c>
       <c r="M6" s="8" t="s">
         <v>16</v>
       </c>
@@ -860,16 +913,34 @@
       <c r="C7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SONY</v>
+      </c>
       <c r="E7" s="4">
         <v>2</v>
       </c>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="G7" s="11">
+        <f t="shared" si="1"/>
+        <v>1700000</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="2"/>
+        <v>3400000</v>
+      </c>
+      <c r="I7" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>DEPOK</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+      <c r="K7" s="12">
+        <f t="shared" si="5"/>
+        <v>3600000</v>
+      </c>
       <c r="M7" s="4" t="s">
         <v>17</v>
       </c>
@@ -884,16 +955,34 @@
       <c r="C8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SHARP</v>
+      </c>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="G8" s="11">
+        <f t="shared" si="1"/>
+        <v>2250000</v>
+      </c>
+      <c r="H8" s="12">
+        <f t="shared" si="2"/>
+        <v>9000000</v>
+      </c>
+      <c r="I8" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>JAKARTA</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="K8" s="12">
+        <f t="shared" si="5"/>
+        <v>9050000</v>
+      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -908,16 +997,34 @@
       <c r="C9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SONY</v>
+      </c>
       <c r="E9" s="4">
         <v>3</v>
       </c>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="G9" s="11">
+        <f t="shared" si="1"/>
+        <v>1200000</v>
+      </c>
+      <c r="H9" s="12">
+        <f t="shared" si="2"/>
+        <v>3600000</v>
+      </c>
+      <c r="I9" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>DEPOK</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+      <c r="K9" s="12">
+        <f t="shared" si="5"/>
+        <v>3800000</v>
+      </c>
       <c r="M9" s="4" t="s">
         <v>19</v>
       </c>
@@ -932,16 +1039,34 @@
       <c r="C10" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SAMSUNG</v>
+      </c>
       <c r="E10" s="4">
         <v>1</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="G10" s="11">
+        <f t="shared" si="1"/>
+        <v>1600000</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="2"/>
+        <v>1600000</v>
+      </c>
+      <c r="I10" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>BEKASI</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="4"/>
+        <v>150000</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="5"/>
+        <v>1750000</v>
+      </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
@@ -950,16 +1075,34 @@
       <c r="C11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>LG</v>
+      </c>
       <c r="E11" s="4">
         <v>3</v>
       </c>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+      <c r="G11" s="11">
+        <f t="shared" si="1"/>
+        <v>2750000</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="2"/>
+        <v>8250000</v>
+      </c>
+      <c r="I11" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>BOGOR</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="4"/>
+        <v>100000</v>
+      </c>
+      <c r="K11" s="12">
+        <f t="shared" si="5"/>
+        <v>8350000</v>
+      </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -968,16 +1111,34 @@
       <c r="C12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SAMSUNG</v>
+      </c>
       <c r="E12" s="4">
         <v>3</v>
       </c>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="G12" s="11">
+        <f t="shared" si="1"/>
+        <v>1150000</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="2"/>
+        <v>3450000</v>
+      </c>
+      <c r="I12" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>JAKARTA</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+      <c r="K12" s="12">
+        <f t="shared" si="5"/>
+        <v>3500000</v>
+      </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
@@ -986,25 +1147,43 @@
       <c r="C13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SONY</v>
+      </c>
       <c r="E13" s="4">
         <v>4</v>
       </c>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="G13" s="11">
+        <f t="shared" si="1"/>
+        <v>2550000</v>
+      </c>
+      <c r="H13" s="12">
+        <f t="shared" si="2"/>
+        <v>10200000</v>
+      </c>
+      <c r="I13" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>DEPOK</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" si="5"/>
+        <v>10400000</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
@@ -1022,13 +1201,13 @@
       <c r="F16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
@@ -1112,11 +1291,11 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
       <c r="H20" s="5" t="s">
         <v>11</v>
       </c>
@@ -1134,11 +1313,11 @@
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1150,7 +1329,7 @@
     <mergeCell ref="B15:F15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B21" r:id="rId1" xr:uid="{CD846EF3-55B6-4891-8F6A-A8CDB3035270}"/>
+    <hyperlink ref="B21" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 6.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 6.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Penjualan 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C420DCDE-008E-4682-916A-F1077BDD2FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="3" r:id="rId1"/>
@@ -24,7 +25,7 @@
     <definedName name="negara">#REF!</definedName>
     <definedName name="UKURAN">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -217,7 +218,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -385,9 +386,6 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -398,6 +396,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -426,9 +427,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -466,9 +467,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -503,7 +504,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -538,7 +539,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -711,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -734,20 +735,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:14" ht="30" x14ac:dyDescent="0.25">
@@ -789,38 +790,20 @@
       <c r="C4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="11" t="str">
-        <f>VLOOKUP(MID(B4,4,2),$M$5:$N$9,2,FALSE)</f>
-        <v>LG</v>
-      </c>
+      <c r="D4" s="11"/>
       <c r="E4" s="4">
         <v>4</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="11">
-        <f>INDEX($H$17:$L$20,MATCH(MID(B4,6,2),$H$17:$H$20,0),MATCH(VLOOKUP(MID(B4,4,2),$M$5:$N$9,2,FALSE),$H$17:$L$17,0))</f>
-        <v>3500000</v>
-      </c>
-      <c r="H4" s="12">
-        <f>G4*E4</f>
-        <v>14000000</v>
-      </c>
-      <c r="I4" s="11" t="str">
-        <f>HLOOKUP(LEFT(B4,3),$B$16:$F$18,2,FALSE)</f>
-        <v>BEKASI</v>
-      </c>
-      <c r="J4" s="12">
-        <f>HLOOKUP(LEFT(B4,3),$B$16:$F$18,3,FALSE)</f>
-        <v>150000</v>
-      </c>
-      <c r="K4" s="12">
-        <f>H4+J4</f>
-        <v>14150000</v>
-      </c>
-      <c r="M4" s="17" t="s">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="M4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="17"/>
+      <c r="N4" s="16"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
@@ -829,34 +812,16 @@
       <c r="C5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="11" t="str">
-        <f t="shared" ref="D5:D13" si="0">VLOOKUP(MID(B5,4,2),$M$5:$N$9,2,FALSE)</f>
-        <v>SHARP</v>
-      </c>
+      <c r="D5" s="11"/>
       <c r="E5" s="4">
         <v>4</v>
       </c>
       <c r="F5" s="11"/>
-      <c r="G5" s="11">
-        <f t="shared" ref="G5:G13" si="1">INDEX($H$17:$L$20,MATCH(MID(B5,6,2),$H$17:$H$20,0),MATCH(VLOOKUP(MID(B5,4,2),$M$5:$N$9,2,FALSE),$H$17:$L$17,0))</f>
-        <v>2250000</v>
-      </c>
-      <c r="H5" s="12">
-        <f t="shared" ref="H5:H13" si="2">G5*E5</f>
-        <v>9000000</v>
-      </c>
-      <c r="I5" s="11" t="str">
-        <f t="shared" ref="I5:I13" si="3">HLOOKUP(LEFT(B5,3),$B$16:$F$18,2,FALSE)</f>
-        <v>JAKARTA</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" ref="J5:J13" si="4">HLOOKUP(LEFT(B5,3),$B$16:$F$18,3,FALSE)</f>
-        <v>50000</v>
-      </c>
-      <c r="K5" s="12">
-        <f t="shared" ref="K5:K13" si="5">H5+J5</f>
-        <v>9050000</v>
-      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
       <c r="M5" s="7" t="s">
         <v>12</v>
       </c>
@@ -871,34 +836,16 @@
       <c r="C6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SAMSUNG</v>
-      </c>
+      <c r="D6" s="11"/>
       <c r="E6" s="4">
         <v>3</v>
       </c>
       <c r="F6" s="11"/>
-      <c r="G6" s="11">
-        <f t="shared" si="1"/>
-        <v>1600000</v>
-      </c>
-      <c r="H6" s="12">
-        <f t="shared" si="2"/>
-        <v>4800000</v>
-      </c>
-      <c r="I6" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>BOGOR</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-      <c r="K6" s="12">
-        <f t="shared" si="5"/>
-        <v>4900000</v>
-      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
       <c r="M6" s="8" t="s">
         <v>16</v>
       </c>
@@ -913,34 +860,16 @@
       <c r="C7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SONY</v>
-      </c>
+      <c r="D7" s="11"/>
       <c r="E7" s="4">
         <v>2</v>
       </c>
       <c r="F7" s="11"/>
-      <c r="G7" s="11">
-        <f t="shared" si="1"/>
-        <v>1700000</v>
-      </c>
-      <c r="H7" s="12">
-        <f t="shared" si="2"/>
-        <v>3400000</v>
-      </c>
-      <c r="I7" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>DEPOK</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-      <c r="K7" s="12">
-        <f t="shared" si="5"/>
-        <v>3600000</v>
-      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
       <c r="M7" s="4" t="s">
         <v>17</v>
       </c>
@@ -955,34 +884,16 @@
       <c r="C8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SHARP</v>
-      </c>
+      <c r="D8" s="11"/>
       <c r="E8" s="4">
         <v>4</v>
       </c>
       <c r="F8" s="11"/>
-      <c r="G8" s="11">
-        <f t="shared" si="1"/>
-        <v>2250000</v>
-      </c>
-      <c r="H8" s="12">
-        <f t="shared" si="2"/>
-        <v>9000000</v>
-      </c>
-      <c r="I8" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>JAKARTA</v>
-      </c>
-      <c r="J8" s="12">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-      <c r="K8" s="12">
-        <f t="shared" si="5"/>
-        <v>9050000</v>
-      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -997,34 +908,16 @@
       <c r="C9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SONY</v>
-      </c>
+      <c r="D9" s="11"/>
       <c r="E9" s="4">
         <v>3</v>
       </c>
       <c r="F9" s="11"/>
-      <c r="G9" s="11">
-        <f t="shared" si="1"/>
-        <v>1200000</v>
-      </c>
-      <c r="H9" s="12">
-        <f t="shared" si="2"/>
-        <v>3600000</v>
-      </c>
-      <c r="I9" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>DEPOK</v>
-      </c>
-      <c r="J9" s="12">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-      <c r="K9" s="12">
-        <f t="shared" si="5"/>
-        <v>3800000</v>
-      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
       <c r="M9" s="4" t="s">
         <v>19</v>
       </c>
@@ -1039,34 +932,16 @@
       <c r="C10" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SAMSUNG</v>
-      </c>
+      <c r="D10" s="11"/>
       <c r="E10" s="4">
         <v>1</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="11">
-        <f t="shared" si="1"/>
-        <v>1600000</v>
-      </c>
-      <c r="H10" s="12">
-        <f t="shared" si="2"/>
-        <v>1600000</v>
-      </c>
-      <c r="I10" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>BEKASI</v>
-      </c>
-      <c r="J10" s="12">
-        <f t="shared" si="4"/>
-        <v>150000</v>
-      </c>
-      <c r="K10" s="12">
-        <f t="shared" si="5"/>
-        <v>1750000</v>
-      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
@@ -1075,34 +950,16 @@
       <c r="C11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>LG</v>
-      </c>
+      <c r="D11" s="11"/>
       <c r="E11" s="4">
         <v>3</v>
       </c>
       <c r="F11" s="11"/>
-      <c r="G11" s="11">
-        <f t="shared" si="1"/>
-        <v>2750000</v>
-      </c>
-      <c r="H11" s="12">
-        <f t="shared" si="2"/>
-        <v>8250000</v>
-      </c>
-      <c r="I11" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>BOGOR</v>
-      </c>
-      <c r="J11" s="12">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-      <c r="K11" s="12">
-        <f t="shared" si="5"/>
-        <v>8350000</v>
-      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -1111,34 +968,16 @@
       <c r="C12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SAMSUNG</v>
-      </c>
+      <c r="D12" s="11"/>
       <c r="E12" s="4">
         <v>3</v>
       </c>
       <c r="F12" s="11"/>
-      <c r="G12" s="11">
-        <f t="shared" si="1"/>
-        <v>1150000</v>
-      </c>
-      <c r="H12" s="12">
-        <f t="shared" si="2"/>
-        <v>3450000</v>
-      </c>
-      <c r="I12" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>JAKARTA</v>
-      </c>
-      <c r="J12" s="12">
-        <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-      <c r="K12" s="12">
-        <f t="shared" si="5"/>
-        <v>3500000</v>
-      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
@@ -1147,43 +986,25 @@
       <c r="C13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>SONY</v>
-      </c>
+      <c r="D13" s="11"/>
       <c r="E13" s="4">
         <v>4</v>
       </c>
       <c r="F13" s="11"/>
-      <c r="G13" s="11">
-        <f t="shared" si="1"/>
-        <v>2550000</v>
-      </c>
-      <c r="H13" s="12">
-        <f t="shared" si="2"/>
-        <v>10200000</v>
-      </c>
-      <c r="I13" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>DEPOK</v>
-      </c>
-      <c r="J13" s="12">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-      <c r="K13" s="12">
-        <f t="shared" si="5"/>
-        <v>10400000</v>
-      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
@@ -1201,13 +1022,13 @@
       <c r="F16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
@@ -1291,11 +1112,11 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
       <c r="H20" s="5" t="s">
         <v>11</v>
       </c>
@@ -1313,11 +1134,11 @@
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1329,7 +1150,7 @@
     <mergeCell ref="B15:F15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B21" r:id="rId1"/>
+    <hyperlink ref="B21" r:id="rId1" xr:uid="{CD846EF3-55B6-4891-8F6A-A8CDB3035270}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
